--- a/docs/dossiers/dossier-paris-13e-b8ea3e87.xlsx
+++ b/docs/dossiers/dossier-paris-13e-b8ea3e87.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 28/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 29/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-13e-b8ea3e87.xlsx
+++ b/docs/dossiers/dossier-paris-13e-b8ea3e87.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 29/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 30/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-13e-b8ea3e87.xlsx
+++ b/docs/dossiers/dossier-paris-13e-b8ea3e87.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 30/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 31/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
